--- a/reference/taiwan_strait_wargame_demo.xlsx
+++ b/reference/taiwan_strait_wargame_demo.xlsx
@@ -2,23 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" r:id="R73be8b33945941dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Public_Sources" sheetId="2" r:id="R015c3df23c2840e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Public_Activity" sheetId="3" r:id="R1453bd4ea104423b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Scenario" sheetId="4" r:id="Rc97e9e832dcf4fc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Actors" sheetId="5" r:id="R10af3bf187814754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Zones" sheetId="6" r:id="R10ce354399c640e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Force_Packages" sheetId="7" r:id="Re200b65398c94bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Capabilities" sheetId="8" r:id="Rcc2851436e2b4cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Weather" sheetId="9" r:id="R7f3d06b805494e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Intelligence" sheetId="10" r:id="R6279c5c96813456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Event_Cards" sheetId="11" r:id="Ra6d2a311fb9d4be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Orders" sheetId="12" r:id="R2ef5e4e12d584b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Engagements" sheetId="13" r:id="R09780f8438ac4eca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Attrition" sheetId="14" r:id="Rba3166ed30d74dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Intercept_Lab" sheetId="15" r:id="Rf44dcae4f8fa4aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_Data_Dictionary" sheetId="16" r:id="R2dd7bfebb07c4857"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_Dashboard" sheetId="17" r:id="Rf3b8bde00ae2431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" r:id="R7707c8ba38e541d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Public_Sources" sheetId="2" r:id="R9395f90f529b43c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Public_Activity" sheetId="3" r:id="R4b4b963af1b84ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Scenario" sheetId="4" r:id="R483d0aa1f2914b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Actors" sheetId="5" r:id="R20d02853c91248a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Zones" sheetId="6" r:id="R7e1f8d4e6eeb4a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Force_Packages" sheetId="7" r:id="R9665b3ca94494d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Capabilities" sheetId="8" r:id="R370723b8cb8c4a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Weather" sheetId="9" r:id="R6c4d0485fc454ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Intelligence" sheetId="10" r:id="R897b531c64e24f63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Event_Cards" sheetId="11" r:id="Rb440503533a249ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Orders" sheetId="12" r:id="R833845684cdc4255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Engagements" sheetId="13" r:id="Ra062671e54974e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Attrition" sheetId="14" r:id="R36192d889462433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Intercept_Lab" sheetId="15" r:id="R998ce643949d408d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_Data_Dictionary" sheetId="16" r:id="R982aa78354594bb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_Dashboard" sheetId="17" r:id="Rf800d79f5fad4745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_Scenario_Templates" sheetId="18" r:id="R528d6d523d904ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_Settings" sheetId="19" r:id="R382459b399fd476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_Resources" sheetId="20" r:id="R7097fef3c7b74c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_Actions" sheetId="21" r:id="R8340f810f8b548ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_LLM_Providers" sheetId="22" r:id="R703ba40a88d2445f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +39,7 @@
     <x:numFmt numFmtId="201" formatCode="0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -56,8 +61,19 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -94,6 +110,26 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF15324B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6674"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F4E4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -102,7 +138,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="64">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -196,6 +232,47 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -203,7 +280,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAF7"/>
         </x:patternFill>
       </x:fill>
@@ -224,17 +301,14 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>各方合成準備指數：前後比較</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:varyColors val="0"/>
@@ -379,25 +453,26 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>回合別合成準備指數</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>BLUE</c:v>
           </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>'16_Dashboard'!$H$11:$H$22</c:f>
@@ -423,6 +498,9 @@
           <c:tx>
             <c:v>RED</c:v>
           </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>'16_Dashboard'!$H$11:$H$22</c:f>
@@ -448,6 +526,9 @@
           <c:tx>
             <c:v>AMBER</c:v>
           </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>'16_Dashboard'!$H$11:$H$22</c:f>
@@ -574,7 +655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R791cf8233d374981"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64d4612aa60d4717"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -604,7 +685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb08c1f1added4a41"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4fc3c60173d3433c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -938,9 +1019,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1090,7 +1171,7 @@
         <x:v>示範情境</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>臺海72小時有限封控與危機管理，包含臺灣、中國大陸、美軍支援及白方導調。</x:v>
+        <x:v>系統現有9種內建情境範本，並同步保存回合順序、戰略壓力、11項資源、行動與LLM供應商設定。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1135,7 +1216,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="30" t="str">
-        <x:v>資料表關聯：Actors → Force_Packages / Orders；Zones → Weather / Intelligence / Engagements；Scenario → Events / AAR</x:v>
+        <x:v>資料表關聯：Scenario_Templates → Settings / Resources / Events；Actors → Force_Packages / Actions / Orders；Zones → Weather / Intelligence / Engagements</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2354,7 +2435,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4321d2d77cb242a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2db4d9e5a60b4cb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2916,13 +2997,136 @@
         <x:v>固定</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="56" t="str">
+        <x:v>EVT-013</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C16" s="56" t="str">
+        <x:v>無人機中繼網路啟用</x:v>
+      </x:c>
+      <x:c r="D16" s="56" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="E16" s="56" t="str">
+        <x:v>Z-ISL</x:v>
+      </x:c>
+      <x:c r="F16" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="G16" s="56" t="str">
+        <x:v>分散式無人機節點提供偵察與通訊中繼，但增加持續運作負荷。</x:v>
+      </x:c>
+      <x:c r="H16" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="56" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="K16" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="56" t="str">
+        <x:v>條件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="60" t="str">
+        <x:v>EVT-014</x:v>
+      </x:c>
+      <x:c r="B17" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C17" s="60" t="str">
+        <x:v>星鏈備援鏈路切換</x:v>
+      </x:c>
+      <x:c r="D17" s="60" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="E17" s="60" t="str">
+        <x:v>Z-REAR</x:v>
+      </x:c>
+      <x:c r="F17" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="G17" s="60" t="str">
+        <x:v>主要鏈路降級後切換至分散式衛星備援通訊。</x:v>
+      </x:c>
+      <x:c r="H17" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="60" t="str">
+        <x:v>條件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="56" t="str">
+        <x:v>EVT-015</x:v>
+      </x:c>
+      <x:c r="B18" s="56" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C18" s="56" t="str">
+        <x:v>高空通訊平臺接替</x:v>
+      </x:c>
+      <x:c r="D18" s="56" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="E18" s="56" t="str">
+        <x:v>Z-REAR</x:v>
+      </x:c>
+      <x:c r="F18" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="G18" s="56" t="str">
+        <x:v>高空平臺接替部分區域通訊中繼，改善跨區協調。</x:v>
+      </x:c>
+      <x:c r="H18" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="56" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="K18" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L18" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="56" t="str">
+        <x:v>條件</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddc91c3d675c4110"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf642d3d7df784929"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4138,7 +4342,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45667ed20c05426d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bbf36f04e68453f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4267,7 +4471,7 @@
       </x:c>
       <x:c r="N4" s="38" t="n">
         <x:f>1-(1-M4)^G4</x:f>
-        <x:v>0.6962131292088696</x:v>
+        <x:v>0.6962131292088695</x:v>
       </x:c>
       <x:c r="O4" s="36" t="str">
         <x:v>防護成功</x:v>
@@ -5564,7 +5768,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ccb52361834c39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cfd8db7de7c42ad"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6886,7 +7090,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd54b72a167240b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ec9f2e18fc14490"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7232,7 +7436,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ff1ff71add54ace"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02f511623444f79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7542,13 +7746,166 @@
         <x:v>合成</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="56" t="str">
+        <x:v>scenario_master</x:v>
+      </x:c>
+      <x:c r="B20" s="56" t="str">
+        <x:v>template_key</x:v>
+      </x:c>
+      <x:c r="C20" s="56" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D20" s="56" t="str">
+        <x:v>對應介面的情境範本代碼</x:v>
+      </x:c>
+      <x:c r="E20" s="56" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="60" t="str">
+        <x:v>scenario_master</x:v>
+      </x:c>
+      <x:c r="B21" s="60" t="str">
+        <x:v>strategic_parameters_json</x:v>
+      </x:c>
+      <x:c r="C21" s="60" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D21" s="60" t="str">
+        <x:v>戰略壓力參數完整設定</x:v>
+      </x:c>
+      <x:c r="E21" s="60" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="56" t="str">
+        <x:v>scenario_master</x:v>
+      </x:c>
+      <x:c r="B22" s="56" t="str">
+        <x:v>resources_json</x:v>
+      </x:c>
+      <x:c r="C22" s="56" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D22" s="56" t="str">
+        <x:v>十一項合成資源預設值</x:v>
+      </x:c>
+      <x:c r="E22" s="56" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="60" t="str">
+        <x:v>setting_catalog</x:v>
+      </x:c>
+      <x:c r="B23" s="60" t="str">
+        <x:v>setting_id</x:v>
+      </x:c>
+      <x:c r="C23" s="60" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D23" s="60" t="str">
+        <x:v>index.html 控制項識別碼</x:v>
+      </x:c>
+      <x:c r="E23" s="60" t="str">
+        <x:v>系統設定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="56" t="str">
+        <x:v>setting_catalog</x:v>
+      </x:c>
+      <x:c r="B24" s="56" t="str">
+        <x:v>option_values_json</x:v>
+      </x:c>
+      <x:c r="C24" s="56" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D24" s="56" t="str">
+        <x:v>選單可用值；動態選單可為空陣列</x:v>
+      </x:c>
+      <x:c r="E24" s="56" t="str">
+        <x:v>系統設定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="60" t="str">
+        <x:v>resource_catalog</x:v>
+      </x:c>
+      <x:c r="B25" s="60" t="str">
+        <x:v>resource_id</x:v>
+      </x:c>
+      <x:c r="C25" s="60" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D25" s="60" t="str">
+        <x:v>與 app.js RESOURCE_DEFAULTS 對應</x:v>
+      </x:c>
+      <x:c r="E25" s="60" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="56" t="str">
+        <x:v>action_catalog</x:v>
+      </x:c>
+      <x:c r="B26" s="56" t="str">
+        <x:v>action_id</x:v>
+      </x:c>
+      <x:c r="C26" s="56" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D26" s="56" t="str">
+        <x:v>與 app.js ACTIONS 對應</x:v>
+      </x:c>
+      <x:c r="E26" s="56" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="60" t="str">
+        <x:v>llm_providers</x:v>
+      </x:c>
+      <x:c r="B27" s="60" t="str">
+        <x:v>endpoint</x:v>
+      </x:c>
+      <x:c r="C27" s="60" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D27" s="60" t="str">
+        <x:v>供應商預設 HTTPS API Endpoint</x:v>
+      </x:c>
+      <x:c r="E27" s="60" t="str">
+        <x:v>系統設定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="56" t="str">
+        <x:v>llm_providers</x:v>
+      </x:c>
+      <x:c r="B28" s="56" t="str">
+        <x:v>api_key_storage</x:v>
+      </x:c>
+      <x:c r="C28" s="56" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D28" s="56" t="str">
+        <x:v>僅記錄保存政策，不保存任何金鑰</x:v>
+      </x:c>
+      <x:c r="E28" s="56" t="str">
+        <x:v>系統設定</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1b2e2f2b754c23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R497b370c5eae4c8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7985,7 +8342,3395 @@
     <x:mergeCell ref="A34:L36"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc93912ee1154e6f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra42f39ca837543e6"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="50" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="50" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="50" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="48" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="50" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="50" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="47" t="str">
+        <x:v>九種內建情境範本與完整預設設定</x:v>
+      </x:c>
+      <x:c r="B1" s="47"/>
+      <x:c r="C1" s="47"/>
+      <x:c r="D1" s="47"/>
+      <x:c r="E1" s="47"/>
+      <x:c r="F1" s="47"/>
+      <x:c r="G1" s="47"/>
+      <x:c r="H1" s="47"/>
+      <x:c r="I1" s="47"/>
+      <x:c r="J1" s="47"/>
+      <x:c r="K1" s="47"/>
+      <x:c r="L1" s="47"/>
+      <x:c r="M1" s="47"/>
+      <x:c r="N1" s="47"/>
+      <x:c r="O1" s="47"/>
+      <x:c r="P1" s="47"/>
+      <x:c r="Q1" s="47"/>
+      <x:c r="R1" s="47"/>
+      <x:c r="S1" s="47"/>
+      <x:c r="T1" s="47"/>
+      <x:c r="U1" s="47"/>
+      <x:c r="V1" s="47"/>
+      <x:c r="W1" s="47"/>
+      <x:c r="X1" s="47"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="52" t="str">
+        <x:v>template_key</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>介面標籤</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="str">
+        <x:v>想定名稱</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="str">
+        <x:v>重點</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="str">
+        <x:v>難度</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>回合</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="str">
+        <x:v>時數/回合</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="str">
+        <x:v>時間範圍</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="str">
+        <x:v>情報不確定度</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="str">
+        <x:v>民事壓力</x:v>
+      </x:c>
+      <x:c r="K3" s="52" t="str">
+        <x:v>外部支援</x:v>
+      </x:c>
+      <x:c r="L3" s="52" t="str">
+        <x:v>天候</x:v>
+      </x:c>
+      <x:c r="M3" s="52" t="str">
+        <x:v>回合順序</x:v>
+      </x:c>
+      <x:c r="N3" s="52" t="str">
+        <x:v>先手公開</x:v>
+      </x:c>
+      <x:c r="O3" s="52" t="str">
+        <x:v>來源/案例</x:v>
+      </x:c>
+      <x:c r="P3" s="52" t="str">
+        <x:v>簡介</x:v>
+      </x:c>
+      <x:c r="Q3" s="52" t="str">
+        <x:v>戰略參數JSON</x:v>
+      </x:c>
+      <x:c r="R3" s="52" t="str">
+        <x:v>資源JSON</x:v>
+      </x:c>
+      <x:c r="S3" s="52" t="str">
+        <x:v>目標JSON</x:v>
+      </x:c>
+      <x:c r="T3" s="52" t="str">
+        <x:v>成功條件JSON</x:v>
+      </x:c>
+      <x:c r="U3" s="52" t="str">
+        <x:v>限制JSON</x:v>
+      </x:c>
+      <x:c r="V3" s="52" t="str">
+        <x:v>參考資料JSON</x:v>
+      </x:c>
+      <x:c r="W3" s="52" t="str">
+        <x:v>事件JSON</x:v>
+      </x:c>
+      <x:c r="X3" s="52" t="str">
+        <x:v>資料分類</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>blockade</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>有限封控與商運壓力（預設）</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>海峽警戒與有限封控：72小時聯合決策演練</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>joint</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="F4" s="56" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G4" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="str">
+        <x:v>T+0至T+72</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="L4" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="M4" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N4" s="56" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O4" s="56" t="str">
+        <x:v>自訂合成想定</x:v>
+      </x:c>
+      <x:c r="P4" s="56" t="str">
+        <x:v>有限封控、商運改道與資訊操作同時出現；各方須在不完整資訊下保存資源並避免危機升級。</x:v>
+      </x:c>
+      <x:c r="Q4" s="56" t="str">
+        <x:v>["維持關鍵海空通道與指揮韌性","在資源有限下平衡防護、後勤與民事需求","辨識升級風險並保留外交空間"]</x:v>
+      </x:c>
+      <x:c r="R4" s="56" t="str">
+        <x:v>["關鍵功能維持在可接受水準","未因單一回合投入耗盡後續資源","能解釋每項決策的假設與替代方案"]</x:v>
+      </x:c>
+      <x:c r="S4" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="T4" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="U4" s="56" t="str">
+        <x:v>{"coercionMode":"limited_blockade","energyReserveDays":30,"residualPowerPct":80,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":1}</x:v>
+      </x:c>
+      <x:c r="V4" s="56" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W4" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="X4" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="60" t="str">
+        <x:v>airdefense</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="str">
+        <x:v>防空資源與預警</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>多軸空情與分層防護：48小時資源配置演練</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="str">
+        <x:v>airdefense</x:v>
+      </x:c>
+      <x:c r="E5" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="F5" s="60" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G5" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H5" s="60" t="str">
+        <x:v>T+0至T+48</x:v>
+      </x:c>
+      <x:c r="I5" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J5" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K5" s="60" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="L5" s="60" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="M5" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N5" s="60" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O5" s="60" t="str">
+        <x:v>自訂合成想定</x:v>
+      </x:c>
+      <x:c r="P5" s="60" t="str">
+        <x:v>多方向空情與合成來襲目標造成警戒壓力，必須在預警、攔截存量與民事影響之間做取捨。</x:v>
+      </x:c>
+      <x:c r="Q5" s="60" t="str">
+        <x:v>["比較預警品質、攔截配置與庫存保留","處理多目標與資訊不確定性","理解單次成功率不等於整體防護效果"]</x:v>
+      </x:c>
+      <x:c r="R5" s="60" t="str">
+        <x:v>["防護任務與庫存風險取得平衡","能說明感測、指管及環境對結果的影響","避免把合成機率視為真實武器性能"]</x:v>
+      </x:c>
+      <x:c r="S5" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="T5" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="U5" s="60" t="str">
+        <x:v>{"coercionMode":"limited_blockade","energyReserveDays":30,"residualPowerPct":80,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":1}</x:v>
+      </x:c>
+      <x:c r="V5" s="60" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W5" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="X5" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="56" t="str">
+        <x:v>logistics</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>後勤優先</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>港口延誤與後勤韌性：96小時持續性演練</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="str">
+        <x:v>logistics</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="F6" s="56" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G6" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="56" t="str">
+        <x:v>T+0至T+96</x:v>
+      </x:c>
+      <x:c r="I6" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J6" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K6" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="L6" s="56" t="str">
+        <x:v>adverse</x:v>
+      </x:c>
+      <x:c r="M6" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N6" s="56" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O6" s="56" t="str">
+        <x:v>自訂合成想定</x:v>
+      </x:c>
+      <x:c r="P6" s="56" t="str">
+        <x:v>港口作業、運輸節點與維修批次陸續受阻；推演重點是優先順序、替代路線與資源保存。</x:v>
+      </x:c>
+      <x:c r="Q6" s="56" t="str">
+        <x:v>["維持補給、維修與運輸節點","在任務壓力下安排修復優先順序","評估民事交通與軍事後勤的衝突"]</x:v>
+      </x:c>
+      <x:c r="R6" s="56" t="str">
+        <x:v>["持續性指數未跌破危險門檻","完成至少一次有效修復或替代路線","提出可驗證的後勤風險指標"]</x:v>
+      </x:c>
+      <x:c r="S6" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="T6" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="U6" s="56" t="str">
+        <x:v>{"coercionMode":"limited_blockade","energyReserveDays":30,"residualPowerPct":80,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":1}</x:v>
+      </x:c>
+      <x:c r="V6" s="56" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W6" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="X6" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="60" t="str">
+        <x:v>grayzone</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="str">
+        <x:v>灰色地帶與資訊迷霧</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>灰色地帶與資訊迷霧：跨域判讀演練</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="str">
+        <x:v>intelligence</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="60" t="str">
+        <x:v>T+0至T+60</x:v>
+      </x:c>
+      <x:c r="I7" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J7" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K7" s="60" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="L7" s="60" t="str">
+        <x:v>stable</x:v>
+      </x:c>
+      <x:c r="M7" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N7" s="60" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O7" s="60" t="str">
+        <x:v>自訂合成想定</x:v>
+      </x:c>
+      <x:c r="P7" s="60" t="str">
+        <x:v>不明海空活動、訊息操作與模糊歸因事件交錯，需區分事實、推測與未知。</x:v>
+      </x:c>
+      <x:c r="Q7" s="60" t="str">
+        <x:v>["區分事實、推測及未知","評估來源可靠度與分析信心","避免以單一訊息直接推導對手意圖"]</x:v>
+      </x:c>
+      <x:c r="R7" s="60" t="str">
+        <x:v>["重大決策引用至少兩項獨立線索","明確標記關鍵假設","能在新情報出現後修正判斷"]</x:v>
+      </x:c>
+      <x:c r="S7" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="T7" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="U7" s="60" t="str">
+        <x:v>{"coercionMode":"limited_blockade","energyReserveDays":30,"residualPowerPct":80,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":1}</x:v>
+      </x:c>
+      <x:c r="V7" s="60" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W7" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="X7" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="56" t="str">
+        <x:v>humanitarian</x:v>
+      </x:c>
+      <x:c r="B8" s="56" t="str">
+        <x:v>人道疏散與民事協調</x:v>
+      </x:c>
+      <x:c r="C8" s="56" t="str">
+        <x:v>人道疏散與民事協調：危機韌性演練</x:v>
+      </x:c>
+      <x:c r="D8" s="56" t="str">
+        <x:v>civil</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="F8" s="56" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H8" s="56" t="str">
+        <x:v>T+0至T+60</x:v>
+      </x:c>
+      <x:c r="I8" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J8" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K8" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="L8" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="M8" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N8" s="56" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O8" s="56" t="str">
+        <x:v>自訂合成想定</x:v>
+      </x:c>
+      <x:c r="P8" s="56" t="str">
+        <x:v>人道需求、商運延誤與公共訊息壓力升高；資源配置需兼顧防護、疏散與基本服務。</x:v>
+      </x:c>
+      <x:c r="Q8" s="56" t="str">
+        <x:v>["維持商運、人道與基礎功能","處理假訊息與群眾焦慮","平衡軍事行動與民事風險"]</x:v>
+      </x:c>
+      <x:c r="R8" s="56" t="str">
+        <x:v>["民事風險未持續失控","建立公開訊息與跨部門協調方案","每回合均評估非軍事後果"]</x:v>
+      </x:c>
+      <x:c r="S8" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="T8" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="U8" s="56" t="str">
+        <x:v>{"coercionMode":"limited_blockade","energyReserveDays":30,"residualPowerPct":80,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":1}</x:v>
+      </x:c>
+      <x:c r="V8" s="56" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W8" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="X8" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="60" t="str">
+        <x:v>deescalation</x:v>
+      </x:c>
+      <x:c r="B9" s="60" t="str">
+        <x:v>危機降溫與外交窗口</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>危機降溫與外交窗口：升級控制演練</x:v>
+      </x:c>
+      <x:c r="D9" s="60" t="str">
+        <x:v>diplomacy</x:v>
+      </x:c>
+      <x:c r="E9" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="F9" s="60" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G9" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H9" s="60" t="str">
+        <x:v>T+0至T+48</x:v>
+      </x:c>
+      <x:c r="I9" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J9" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K9" s="60" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="L9" s="60" t="str">
+        <x:v>stable</x:v>
+      </x:c>
+      <x:c r="M9" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N9" s="60" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O9" s="60" t="str">
+        <x:v>自訂合成想定</x:v>
+      </x:c>
+      <x:c r="P9" s="60" t="str">
+        <x:v>高風險互動後出現有限降溫窗口，需將資源使用、公開訊息與外交協調連成一致策略。</x:v>
+      </x:c>
+      <x:c r="Q9" s="60" t="str">
+        <x:v>["辨識可能觸發升級的行動","利用外交訊號及有限承諾創造降溫窗口","評估外部支援的政治限制"]</x:v>
+      </x:c>
+      <x:c r="R9" s="60" t="str">
+        <x:v>["保留至少一條降溫或談判路徑","避免只以戰果衡量任務成果","能說明軍事與政治目標的關係"]</x:v>
+      </x:c>
+      <x:c r="S9" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="T9" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="U9" s="60" t="str">
+        <x:v>{"coercionMode":"limited_blockade","energyReserveDays":30,"residualPowerPct":80,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":1}</x:v>
+      </x:c>
+      <x:c r="V9" s="60" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W9" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="X9" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="56" t="str">
+        <x:v>csis_blackout_2025</x:v>
+      </x:c>
+      <x:c r="B10" s="56" t="str">
+        <x:v>CSIS《燈火管制》（2025）：封鎖與能源韌性</x:v>
+      </x:c>
+      <x:c r="C10" s="56" t="str">
+        <x:v>CSIS《燈火管制》（2025）：封鎖、護航與能源韌性</x:v>
+      </x:c>
+      <x:c r="D10" s="56" t="str">
+        <x:v>logistics</x:v>
+      </x:c>
+      <x:c r="E10" s="56" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="F10" s="56" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G10" s="56" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H10" s="56" t="str">
+        <x:v>T+0至T+240</x:v>
+      </x:c>
+      <x:c r="I10" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J10" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K10" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="L10" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="M10" s="56" t="str">
+        <x:v>red_first</x:v>
+      </x:c>
+      <x:c r="N10" s="56" t="str">
+        <x:v>public</x:v>
+      </x:c>
+      <x:c r="O10" s="56" t="str">
+        <x:v>CSIS《燈火管制：中國封鎖台灣兵推》（2025）案例假設</x:v>
+      </x:c>
+      <x:c r="P10" s="56" t="str">
+        <x:v>共軍以海警與海上民兵執法為由切斷航運，美日協調護航破封；推演核心是商運持續、能源配給與避免灰色地帶危機失控。</x:v>
+      </x:c>
+      <x:c r="Q10" s="56" t="str">
+        <x:v>["維持最低限度商運與能源輸入","協調多國護航、港口與保險機制","在執法封控敘事下控制升級風險"]</x:v>
+      </x:c>
+      <x:c r="R10" s="56" t="str">
+        <x:v>["第10日仍維持關鍵民生與指揮用電","建立可持續且可解釋的商船護航機制","能源配給未使民事風險持續失控"]</x:v>
+      </x:c>
+      <x:c r="S10" s="56" t="str">
+        <x:v>["案例假設：LNG安全存量於封鎖後10天耗盡。","案例假設：能源耗盡後電力降至平時35%。"]</x:v>
+      </x:c>
+      <x:c r="T10" s="56" t="str">
+        <x:v>[{"title":"CSIS — Lights Out? Wargaming a Chinese Blockade of Taiwan","url":"https://www.csis.org/analysis/lights-out-wargaming-chinese-blockade-taiwan"}]</x:v>
+      </x:c>
+      <x:c r="U10" s="56" t="str">
+        <x:v>{"coercionMode":"law_enforcement_blockade","energyReserveDays":10,"residualPowerPct":35,"precisionStockpileDays":30,"nuclearStrikeCount":0,"globalEconomicShock":4}</x:v>
+      </x:c>
+      <x:c r="V10" s="56" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W10" s="56" t="str">
+        <x:v>[{"trigger_turn":2,"event_name":"海警宣布擴大臨檢","category":"封控","zone_id":"Z-CW","affected_actor":"ALL","description":"以執法名義提高商船進出與保險壓力。","sustainment_delta":-3,"civilian_risk_delta":5},{"trigger_turn":10,"event_name":"護航破封協調窗口","category":"外交","zone_id":"Z-REAR","affected_actor":"AMBER","description":"美日與商運單位研議多國護航及航運風險分攤。","command_delta":4,"sustainment_delta":3},{"trigger_turn":20,"event_name":"能源安全存量耗盡","category":"能源","zone_id":"Z-ISL","affected_actor":"BLUE","description":"案例假設下LNG安全存量耗盡，電力供應面臨快速下降。","readiness_delta":-12,"sustainment_delta":-18,"command_delta":-4,"civilian_risk_delta":18}]</x:v>
+      </x:c>
+      <x:c r="X10" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="60" t="str">
+        <x:v>csis_mit_nuclear_2024</x:v>
+      </x:c>
+      <x:c r="B11" s="60" t="str">
+        <x:v>CSIS &amp; MIT（2024）：核升級風險</x:v>
+      </x:c>
+      <x:c r="C11" s="60" t="str">
+        <x:v>CSIS &amp; MIT（2024）：傳統戰局與核升級風險</x:v>
+      </x:c>
+      <x:c r="D11" s="60" t="str">
+        <x:v>diplomacy</x:v>
+      </x:c>
+      <x:c r="E11" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="F11" s="60" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G11" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H11" s="60" t="str">
+        <x:v>T+0至T+72</x:v>
+      </x:c>
+      <x:c r="I11" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J11" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K11" s="60" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="L11" s="60" t="str">
+        <x:v>stable</x:v>
+      </x:c>
+      <x:c r="M11" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="N11" s="60" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O11" s="60" t="str">
+        <x:v>CSIS &amp; MIT《台海衝突納入核武推演》（2024）案例假設</x:v>
+      </x:c>
+      <x:c r="P11" s="60" t="str">
+        <x:v>傳統戰局對中方不利後，危機跨越核門檻；推演聚焦預警判讀、政治溝通、分散韌性與終止衝突，不處理核武目標或運用細節。</x:v>
+      </x:c>
+      <x:c r="Q11" s="60" t="str">
+        <x:v>["辨識核升級警訊並保留溝通管道","維持最低限度指揮與民事應變功能","建立衝突終止與避免後續升級的政策選項"]</x:v>
+      </x:c>
+      <x:c r="R11" s="60" t="str">
+        <x:v>["在核門檻前提出可信的降溫方案","核事件後維持跨部門指揮與公共訊息","決策未以報復交換取代政治目標"]</x:v>
+      </x:c>
+      <x:c r="S11" s="60" t="str">
+        <x:v>["只採抽象核風險裁決，不呈現目標、武器、當量或運用方式。","案例假設：傳統戰局不利時發生7次戰術核武攻擊。"]</x:v>
+      </x:c>
+      <x:c r="T11" s="60" t="str">
+        <x:v>[{"title":"CSIS — Confronting Armageddon","url":"https://www.csis.org/analysis/confronting-armageddon"},{"title":"MIT Security Studies Program — Flagship Games","url":"https://ssp.mit.edu/wargaming-lab/flagship-games"}]</x:v>
+      </x:c>
+      <x:c r="U11" s="60" t="str">
+        <x:v>{"coercionMode":"nuclear_escalation","energyReserveDays":20,"residualPowerPct":50,"precisionStockpileDays":14,"nuclearStrikeCount":7,"globalEconomicShock":5}</x:v>
+      </x:c>
+      <x:c r="V11" s="60" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W11" s="60" t="str">
+        <x:v>[{"trigger_turn":6,"event_name":"核升級警訊增強","category":"戰略預警","zone_id":"Z-REAR","affected_actor":"ALL","description":"情報顯示核門檻風險顯著升高，外交與危機溝通窗口縮小。","command_delta":-5,"civilian_risk_delta":12},{"trigger_turn":8,"event_name":"七次戰術核武攻擊（抽象裁決）","category":"核升級","zone_id":"Z-ISL","affected_actor":"ALL","description":"依案例假設進行整體性衝擊裁決；不包含目標、武器或運用細節。","readiness_delta":-25,"sustainment_delta":-25,"command_delta":-20,"civilian_risk_delta":40}]</x:v>
+      </x:c>
+      <x:c r="X11" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="56" t="str">
+        <x:v>cnas_policy_war</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="str">
+        <x:v>美國國會 × CNAS：彈藥與全球經濟衝擊</x:v>
+      </x:c>
+      <x:c r="C12" s="56" t="str">
+        <x:v>美國國會 × CNAS：一週彈藥耗盡與全球經濟衝擊</x:v>
+      </x:c>
+      <x:c r="D12" s="56" t="str">
+        <x:v>joint</x:v>
+      </x:c>
+      <x:c r="E12" s="56" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="F12" s="56" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G12" s="56" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H12" s="56" t="str">
+        <x:v>T+0至T+168</x:v>
+      </x:c>
+      <x:c r="I12" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J12" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K12" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="L12" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="M12" s="56" t="str">
+        <x:v>red_first</x:v>
+      </x:c>
+      <x:c r="N12" s="56" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="O12" s="56" t="str">
+        <x:v>美國國會與新美國安全中心（CNAS）政策級兵推案例假設</x:v>
+      </x:c>
+      <x:c r="P12" s="56" t="str">
+        <x:v>政策級推演聚焦開戰後一週內遠程精準導引彈藥耗盡，以及航運、金融、能源與科技供應鏈引發的全球連鎖經濟衝擊。</x:v>
+      </x:c>
+      <x:c r="Q12" s="56" t="str">
+        <x:v>["在一週彈藥限制下設定可持續的政治與軍事優先序","協調工業補充、盟友分工與供應鏈替代","管理全球金融、航運與民生連鎖風險"]</x:v>
+      </x:c>
+      <x:c r="R12" s="56" t="str">
+        <x:v>["第7日仍保有關鍵任務所需資源","建立工業補充與盟友分攤方案","全球經濟衝擊未使政策目標失去可持續性"]</x:v>
+      </x:c>
+      <x:c r="S12" s="56" t="str">
+        <x:v>["案例假設：開戰後一週內耗盡遠程精準導引彈藥。","每回合必須同時評估全球經濟與民事後果。"]</x:v>
+      </x:c>
+      <x:c r="T12" s="56" t="str">
+        <x:v>[{"title":"CNAS — Bad Blood: The TTX for the House Select Committee on the CCP","url":"https://www.cnas.org/publications/congressional-testimony/bad-blood-ttx"}]</x:v>
+      </x:c>
+      <x:c r="U12" s="56" t="str">
+        <x:v>{"coercionMode":"conventional_conflict","energyReserveDays":14,"residualPowerPct":45,"precisionStockpileDays":7,"nuclearStrikeCount":0,"globalEconomicShock":5}</x:v>
+      </x:c>
+      <x:c r="V12" s="56" t="str">
+        <x:v>{"blueAircraft":48,"blueInterceptors":160,"blueVessels":14,"blueLogistics":72,"blueDrones":120,"starlinkNodes":24,"highAltitudePlatforms":6,"redAircraft":96,"redIncoming":180,"redVessels":24,"redLogistics":84}</x:v>
+      </x:c>
+      <x:c r="W12" s="56" t="str">
+        <x:v>[{"trigger_turn":6,"event_name":"全球金融與航運震盪","category":"經濟","zone_id":"Z-REAR","affected_actor":"ALL","description":"保險、金融、能源與科技供應鏈出現跨區域連鎖壓力。","sustainment_delta":-8,"command_delta":-3,"civilian_risk_delta":15},{"trigger_turn":14,"event_name":"遠程精準彈藥耗盡","category":"後勤","zone_id":"Z-REAR","affected_actor":"AMBER","description":"案例假設下，一週後遠程精準導引彈藥存量耗盡。","readiness_delta":-18,"sustainment_delta":-20,"command_delta":-5}]</x:v>
+      </x:c>
+      <x:c r="X12" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:X1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="46" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="52" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="47" t="str">
+        <x:v>目前介面全部設定控制項目錄</x:v>
+      </x:c>
+      <x:c r="B1" s="47"/>
+      <x:c r="C1" s="47"/>
+      <x:c r="D1" s="47"/>
+      <x:c r="E1" s="47"/>
+      <x:c r="F1" s="47"/>
+      <x:c r="G1" s="47"/>
+      <x:c r="H1" s="47"/>
+      <x:c r="I1" s="47"/>
+      <x:c r="J1" s="47"/>
+      <x:c r="K1" s="47"/>
+      <x:c r="L1" s="47"/>
+      <x:c r="M1" s="47"/>
+      <x:c r="N1" s="47"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="52" t="str">
+        <x:v>setting_id</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>介面區段</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="str">
+        <x:v>設定名稱</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="str">
+        <x:v>控制類型</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="str">
+        <x:v>預設值</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>最小值</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="str">
+        <x:v>最大值</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="str">
+        <x:v>步進</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="str">
+        <x:v>選項值JSON</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="str">
+        <x:v>選項標籤JSON</x:v>
+      </x:c>
+      <x:c r="K3" s="52" t="str">
+        <x:v>預設停用</x:v>
+      </x:c>
+      <x:c r="L3" s="52" t="str">
+        <x:v>敏感資料</x:v>
+      </x:c>
+      <x:c r="M3" s="52" t="str">
+        <x:v>來源</x:v>
+      </x:c>
+      <x:c r="N3" s="52" t="str">
+        <x:v>備註</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>importInput</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>global</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>匯入 JSON</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>file</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="str"/>
+      <x:c r="F4" s="56"/>
+      <x:c r="G4" s="56"/>
+      <x:c r="H4" s="56"/>
+      <x:c r="I4" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L4" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N4" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="60" t="str">
+        <x:v>scenarioTemplate</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>情境範本</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E5" s="60" t="str">
+        <x:v>blockade</x:v>
+      </x:c>
+      <x:c r="F5" s="60"/>
+      <x:c r="G5" s="60"/>
+      <x:c r="H5" s="60"/>
+      <x:c r="I5" s="60" t="str">
+        <x:v>["blockade","airdefense","logistics","grayzone","humanitarian","deescalation","csis_blackout_2025","csis_mit_nuclear_2024","cnas_policy_war"]</x:v>
+      </x:c>
+      <x:c r="J5" s="60" t="str">
+        <x:v>["有限封控與商運壓力（預設）","多軸空情與分層防護","港口延誤與後勤韌性","灰色地帶與資訊迷霧","人道疏散與民事協調","危機降溫與外交窗口","CSIS《燈火管制》（2025）：封鎖與能源韌性","CSIS &amp; MIT（2024）：核升級風險","美國國會 × CNAS：彈藥與全球經濟衝擊"]</x:v>
+      </x:c>
+      <x:c r="K5" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N5" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="56" t="str">
+        <x:v>scenarioName</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>想定名稱</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="str">
+        <x:v>海峽警戒與有限封控：72小時聯合決策演練</x:v>
+      </x:c>
+      <x:c r="F6" s="56"/>
+      <x:c r="G6" s="56"/>
+      <x:c r="H6" s="56"/>
+      <x:c r="I6" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J6" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K6" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N6" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="60" t="str">
+        <x:v>scenarioSeed</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>隨機種子</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="str">
+        <x:v>20260727</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="60"/>
+      <x:c r="H7" s="60"/>
+      <x:c r="I7" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J7" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K7" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N7" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="56" t="str">
+        <x:v>focus</x:v>
+      </x:c>
+      <x:c r="B8" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C8" s="56" t="str">
+        <x:v>推演重點</x:v>
+      </x:c>
+      <x:c r="D8" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="str">
+        <x:v>joint</x:v>
+      </x:c>
+      <x:c r="F8" s="56"/>
+      <x:c r="G8" s="56"/>
+      <x:c r="H8" s="56"/>
+      <x:c r="I8" s="56" t="str">
+        <x:v>["joint","airdefense","logistics","intelligence","civil","diplomacy"]</x:v>
+      </x:c>
+      <x:c r="J8" s="56" t="str">
+        <x:v>["聯合決策與整體情勢","防空資源與預警","後勤持續性與修復","情報判讀與戰場迷霧","民事韌性與危機溝通","升級控制與外交協調"]</x:v>
+      </x:c>
+      <x:c r="K8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N8" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="60" t="str">
+        <x:v>difficulty</x:v>
+      </x:c>
+      <x:c r="B9" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>難度</x:v>
+      </x:c>
+      <x:c r="D9" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E9" s="60" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="F9" s="60"/>
+      <x:c r="G9" s="60"/>
+      <x:c r="H9" s="60"/>
+      <x:c r="I9" s="60" t="str">
+        <x:v>["intro","standard","advanced"]</x:v>
+      </x:c>
+      <x:c r="J9" s="60" t="str">
+        <x:v>["基礎","標準","進階"]</x:v>
+      </x:c>
+      <x:c r="K9" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N9" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="56" t="str">
+        <x:v>turns</x:v>
+      </x:c>
+      <x:c r="B10" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C10" s="56" t="str">
+        <x:v>回合數</x:v>
+      </x:c>
+      <x:c r="D10" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E10" s="56" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F10" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="56" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H10" s="56"/>
+      <x:c r="I10" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J10" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K10" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N10" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="60" t="str">
+        <x:v>hoursPerTurn</x:v>
+      </x:c>
+      <x:c r="B11" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C11" s="60" t="str">
+        <x:v>每回合時數</x:v>
+      </x:c>
+      <x:c r="D11" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E11" s="60" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F11" s="60"/>
+      <x:c r="G11" s="60"/>
+      <x:c r="H11" s="60"/>
+      <x:c r="I11" s="60" t="str">
+        <x:v>["3","6","12"]</x:v>
+      </x:c>
+      <x:c r="J11" s="60" t="str">
+        <x:v>["3小時","6小時","12小時"]</x:v>
+      </x:c>
+      <x:c r="K11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N11" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="56" t="str">
+        <x:v>uncertainty</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C12" s="56" t="str">
+        <x:v>情報不確定度</x:v>
+      </x:c>
+      <x:c r="D12" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E12" s="56" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F12" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H12" s="56"/>
+      <x:c r="I12" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J12" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K12" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N12" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="60" t="str">
+        <x:v>civilPressure</x:v>
+      </x:c>
+      <x:c r="B13" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C13" s="60" t="str">
+        <x:v>民事壓力</x:v>
+      </x:c>
+      <x:c r="D13" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E13" s="60" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F13" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H13" s="60"/>
+      <x:c r="I13" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J13" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K13" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N13" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="56" t="str">
+        <x:v>amberSupport</x:v>
+      </x:c>
+      <x:c r="B14" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C14" s="56" t="str">
+        <x:v>美軍支援程度</x:v>
+      </x:c>
+      <x:c r="D14" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E14" s="56" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="F14" s="56"/>
+      <x:c r="G14" s="56"/>
+      <x:c r="H14" s="56"/>
+      <x:c r="I14" s="56" t="str">
+        <x:v>["none","indirect","limited"]</x:v>
+      </x:c>
+      <x:c r="J14" s="56" t="str">
+        <x:v>["不納入","間接支援：ISR、後勤、外交","有限海空存在與防護支援"]</x:v>
+      </x:c>
+      <x:c r="K14" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N14" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="60" t="str">
+        <x:v>weatherPreset</x:v>
+      </x:c>
+      <x:c r="B15" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C15" s="60" t="str">
+        <x:v>初始天候</x:v>
+      </x:c>
+      <x:c r="D15" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E15" s="60" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="F15" s="60"/>
+      <x:c r="G15" s="60"/>
+      <x:c r="H15" s="60"/>
+      <x:c r="I15" s="60" t="str">
+        <x:v>["stable","variable","adverse"]</x:v>
+      </x:c>
+      <x:c r="J15" s="60" t="str">
+        <x:v>["穩定","多變","不利"]</x:v>
+      </x:c>
+      <x:c r="K15" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N15" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="56" t="str">
+        <x:v>turnOrderMode</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C16" s="56" t="str">
+        <x:v>回合行動順序</x:v>
+      </x:c>
+      <x:c r="D16" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E16" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="F16" s="56"/>
+      <x:c r="G16" s="56"/>
+      <x:c r="H16" s="56"/>
+      <x:c r="I16" s="56" t="str">
+        <x:v>["simultaneous","red_first","alternating"]</x:v>
+      </x:c>
+      <x:c r="J16" s="56" t="str">
+        <x:v>["同時密封提交（預設）","紅方先行","輪替先行"]</x:v>
+      </x:c>
+      <x:c r="K16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N16" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="60" t="str">
+        <x:v>firstOrderVisibility</x:v>
+      </x:c>
+      <x:c r="B17" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C17" s="60" t="str">
+        <x:v>先行命令是否公開</x:v>
+      </x:c>
+      <x:c r="D17" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E17" s="60" t="str">
+        <x:v>sealed</x:v>
+      </x:c>
+      <x:c r="F17" s="60"/>
+      <x:c r="G17" s="60"/>
+      <x:c r="H17" s="60"/>
+      <x:c r="I17" s="60" t="str">
+        <x:v>["sealed","public"]</x:v>
+      </x:c>
+      <x:c r="J17" s="60" t="str">
+        <x:v>["不公開：只決定裁決順序","公開：後手可見先手行動"]</x:v>
+      </x:c>
+      <x:c r="K17" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N17" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="56" t="str">
+        <x:v>coercionMode</x:v>
+      </x:c>
+      <x:c r="B18" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C18" s="56" t="str">
+        <x:v>封控／衝突型態</x:v>
+      </x:c>
+      <x:c r="D18" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E18" s="56" t="str">
+        <x:v>limited_blockade</x:v>
+      </x:c>
+      <x:c r="F18" s="56"/>
+      <x:c r="G18" s="56"/>
+      <x:c r="H18" s="56"/>
+      <x:c r="I18" s="56" t="str">
+        <x:v>["limited_blockade","law_enforcement_blockade","conventional_conflict","nuclear_escalation"]</x:v>
+      </x:c>
+      <x:c r="J18" s="56" t="str">
+        <x:v>["有限封控","海警與海上民兵執法封控","傳統軍事衝突","核升級風險情境"]</x:v>
+      </x:c>
+      <x:c r="K18" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N18" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="60" t="str">
+        <x:v>energyReserveDays</x:v>
+      </x:c>
+      <x:c r="B19" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C19" s="60" t="str">
+        <x:v>能源安全存量（天）</x:v>
+      </x:c>
+      <x:c r="D19" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E19" s="60" t="str">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="60" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H19" s="60"/>
+      <x:c r="I19" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J19" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N19" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="56" t="str">
+        <x:v>residualPowerPct</x:v>
+      </x:c>
+      <x:c r="B20" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C20" s="56" t="str">
+        <x:v>能源耗盡後電力（%）</x:v>
+      </x:c>
+      <x:c r="D20" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E20" s="56" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F20" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="56" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H20" s="56"/>
+      <x:c r="I20" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J20" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K20" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N20" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="60" t="str">
+        <x:v>precisionStockpileDays</x:v>
+      </x:c>
+      <x:c r="B21" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C21" s="60" t="str">
+        <x:v>遠程精準彈藥存量（天）</x:v>
+      </x:c>
+      <x:c r="D21" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E21" s="60" t="str">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F21" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="60" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H21" s="60"/>
+      <x:c r="I21" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J21" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K21" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N21" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="56" t="str">
+        <x:v>nuclearStrikeCount</x:v>
+      </x:c>
+      <x:c r="B22" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C22" s="56" t="str">
+        <x:v>戰術核攻擊次數（抽象）</x:v>
+      </x:c>
+      <x:c r="D22" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E22" s="56" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="56" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H22" s="56"/>
+      <x:c r="I22" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J22" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K22" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N22" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="60" t="str">
+        <x:v>globalEconomicShock</x:v>
+      </x:c>
+      <x:c r="B23" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C23" s="60" t="str">
+        <x:v>全球經濟衝擊（1–5）</x:v>
+      </x:c>
+      <x:c r="D23" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E23" s="60" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H23" s="60"/>
+      <x:c r="I23" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J23" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N23" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="56" t="str">
+        <x:v>blueAircraft</x:v>
+      </x:c>
+      <x:c r="B24" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C24" s="56" t="str">
+        <x:v>藍方可用航空架次</x:v>
+      </x:c>
+      <x:c r="D24" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E24" s="56" t="str">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F24" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="56" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H24" s="56"/>
+      <x:c r="I24" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J24" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K24" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N24" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="60" t="str">
+        <x:v>blueInterceptors</x:v>
+      </x:c>
+      <x:c r="B25" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C25" s="60" t="str">
+        <x:v>藍方攔截彈庫存</x:v>
+      </x:c>
+      <x:c r="D25" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E25" s="60" t="str">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="60" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H25" s="60"/>
+      <x:c r="I25" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J25" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N25" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="56" t="str">
+        <x:v>blueVessels</x:v>
+      </x:c>
+      <x:c r="B26" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C26" s="56" t="str">
+        <x:v>藍方海上巡防平台</x:v>
+      </x:c>
+      <x:c r="D26" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E26" s="56" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="56" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H26" s="56"/>
+      <x:c r="I26" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J26" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K26" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N26" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="60" t="str">
+        <x:v>blueLogistics</x:v>
+      </x:c>
+      <x:c r="B27" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C27" s="60" t="str">
+        <x:v>藍方後勤補給批次</x:v>
+      </x:c>
+      <x:c r="D27" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E27" s="60" t="str">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="60" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H27" s="60"/>
+      <x:c r="I27" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J27" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N27" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="56" t="str">
+        <x:v>blueDrones</x:v>
+      </x:c>
+      <x:c r="B28" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C28" s="56" t="str">
+        <x:v>藍方無人機任務批次</x:v>
+      </x:c>
+      <x:c r="D28" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E28" s="56" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F28" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" s="56" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H28" s="56"/>
+      <x:c r="I28" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J28" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K28" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N28" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="60" t="str">
+        <x:v>starlinkNodes</x:v>
+      </x:c>
+      <x:c r="B29" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C29" s="60" t="str">
+        <x:v>星鏈備援通訊節點</x:v>
+      </x:c>
+      <x:c r="D29" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E29" s="60" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F29" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="60" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H29" s="60"/>
+      <x:c r="I29" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J29" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K29" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N29" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="56" t="str">
+        <x:v>highAltitudePlatforms</x:v>
+      </x:c>
+      <x:c r="B30" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C30" s="56" t="str">
+        <x:v>高空通訊平臺</x:v>
+      </x:c>
+      <x:c r="D30" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E30" s="56" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F30" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="56" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H30" s="56"/>
+      <x:c r="I30" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J30" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K30" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N30" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="60" t="str">
+        <x:v>redAircraft</x:v>
+      </x:c>
+      <x:c r="B31" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C31" s="60" t="str">
+        <x:v>紅方航空架次</x:v>
+      </x:c>
+      <x:c r="D31" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E31" s="60" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F31" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="60" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="H31" s="60"/>
+      <x:c r="I31" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J31" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K31" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N31" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="56" t="str">
+        <x:v>redIncoming</x:v>
+      </x:c>
+      <x:c r="B32" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C32" s="56" t="str">
+        <x:v>紅方合成來襲目標</x:v>
+      </x:c>
+      <x:c r="D32" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E32" s="56" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F32" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="56" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H32" s="56"/>
+      <x:c r="I32" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J32" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K32" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N32" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="60" t="str">
+        <x:v>redVessels</x:v>
+      </x:c>
+      <x:c r="B33" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C33" s="60" t="str">
+        <x:v>紅方海上平台</x:v>
+      </x:c>
+      <x:c r="D33" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E33" s="60" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F33" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" s="60" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H33" s="60"/>
+      <x:c r="I33" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J33" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K33" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L33" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M33" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N33" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="56" t="str">
+        <x:v>redLogistics</x:v>
+      </x:c>
+      <x:c r="B34" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C34" s="56" t="str">
+        <x:v>紅方後勤補給批次</x:v>
+      </x:c>
+      <x:c r="D34" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E34" s="56" t="str">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F34" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="56" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H34" s="56"/>
+      <x:c r="I34" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J34" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K34" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N34" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="60" t="str">
+        <x:v>teacherConstraints</x:v>
+      </x:c>
+      <x:c r="B35" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C35" s="60" t="str">
+        <x:v>補充限制</x:v>
+      </x:c>
+      <x:c r="D35" s="60" t="str">
+        <x:v>textarea</x:v>
+      </x:c>
+      <x:c r="E35" s="60" t="str">
+        <x:v>避免升高衝突；需保留後續回合資源；納入商船、人道與資訊環境。</x:v>
+      </x:c>
+      <x:c r="F35" s="60"/>
+      <x:c r="G35" s="60"/>
+      <x:c r="H35" s="60"/>
+      <x:c r="I35" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J35" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K35" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N35" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="56" t="str">
+        <x:v>llmProvider</x:v>
+      </x:c>
+      <x:c r="B36" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C36" s="56" t="str">
+        <x:v>供應商</x:v>
+      </x:c>
+      <x:c r="D36" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E36" s="56" t="str">
+        <x:v>gemini</x:v>
+      </x:c>
+      <x:c r="F36" s="56"/>
+      <x:c r="G36" s="56"/>
+      <x:c r="H36" s="56"/>
+      <x:c r="I36" s="56" t="str">
+        <x:v>["gemini","openai","claude","cgu"]</x:v>
+      </x:c>
+      <x:c r="J36" s="56" t="str">
+        <x:v>["Google Gemini","OpenAI","Anthropic Claude","CGU／相容 API"]</x:v>
+      </x:c>
+      <x:c r="K36" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N36" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="60" t="str">
+        <x:v>llmModel</x:v>
+      </x:c>
+      <x:c r="B37" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C37" s="60" t="str">
+        <x:v>模型名稱</x:v>
+      </x:c>
+      <x:c r="D37" s="60" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="E37" s="60" t="str">
+        <x:v>gemini-3.5-flash</x:v>
+      </x:c>
+      <x:c r="F37" s="60"/>
+      <x:c r="G37" s="60"/>
+      <x:c r="H37" s="60"/>
+      <x:c r="I37" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J37" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K37" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N37" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="56" t="str">
+        <x:v>llmReasoning</x:v>
+      </x:c>
+      <x:c r="B38" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C38" s="56" t="str">
+        <x:v>思考力度</x:v>
+      </x:c>
+      <x:c r="D38" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E38" s="56" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="F38" s="56"/>
+      <x:c r="G38" s="56"/>
+      <x:c r="H38" s="56"/>
+      <x:c r="I38" s="56" t="str">
+        <x:v>["minimal","low","medium","high"]</x:v>
+      </x:c>
+      <x:c r="J38" s="56" t="str">
+        <x:v>["最小","低","中","高"]</x:v>
+      </x:c>
+      <x:c r="K38" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N38" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="60" t="str">
+        <x:v>llmApiKey</x:v>
+      </x:c>
+      <x:c r="B39" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C39" s="60" t="str">
+        <x:v>API Key</x:v>
+      </x:c>
+      <x:c r="D39" s="60" t="str">
+        <x:v>password</x:v>
+      </x:c>
+      <x:c r="E39" s="60" t="str"/>
+      <x:c r="F39" s="60"/>
+      <x:c r="G39" s="60"/>
+      <x:c r="H39" s="60"/>
+      <x:c r="I39" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J39" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K39" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L39" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M39" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N39" s="60" t="str">
+        <x:v>僅保存空白預設；實際金鑰不得寫入資料庫。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="56" t="str">
+        <x:v>llmEndpoint</x:v>
+      </x:c>
+      <x:c r="B40" s="56" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C40" s="56" t="str">
+        <x:v>API Endpoint</x:v>
+      </x:c>
+      <x:c r="D40" s="56" t="str">
+        <x:v>url</x:v>
+      </x:c>
+      <x:c r="E40" s="56" t="str">
+        <x:v>https://generativelanguage.googleapis.com/v1beta</x:v>
+      </x:c>
+      <x:c r="F40" s="56"/>
+      <x:c r="G40" s="56"/>
+      <x:c r="H40" s="56"/>
+      <x:c r="I40" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J40" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K40" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N40" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="60" t="str">
+        <x:v>llmInstruction</x:v>
+      </x:c>
+      <x:c r="B41" s="60" t="str">
+        <x:v>builder</x:v>
+      </x:c>
+      <x:c r="C41" s="60" t="str">
+        <x:v>額外敘事指示（選填）</x:v>
+      </x:c>
+      <x:c r="D41" s="60" t="str">
+        <x:v>textarea</x:v>
+      </x:c>
+      <x:c r="E41" s="60" t="str"/>
+      <x:c r="F41" s="60"/>
+      <x:c r="G41" s="60"/>
+      <x:c r="H41" s="60"/>
+      <x:c r="I41" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J41" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K41" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L41" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M41" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N41" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="56" t="str">
+        <x:v>orderActor</x:v>
+      </x:c>
+      <x:c r="B42" s="56" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C42" s="56" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D42" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E42" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="F42" s="56"/>
+      <x:c r="G42" s="56"/>
+      <x:c r="H42" s="56"/>
+      <x:c r="I42" s="56" t="str">
+        <x:v>["BLUE","RED","AMBER"]</x:v>
+      </x:c>
+      <x:c r="J42" s="56" t="str">
+        <x:v>["藍方（臺灣）","紅方（中國大陸）","琥珀方（美軍支援）"]</x:v>
+      </x:c>
+      <x:c r="K42" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N42" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="60" t="str">
+        <x:v>orderAction</x:v>
+      </x:c>
+      <x:c r="B43" s="60" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C43" s="60" t="str">
+        <x:v>行動</x:v>
+      </x:c>
+      <x:c r="D43" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E43" s="60" t="str"/>
+      <x:c r="F43" s="60"/>
+      <x:c r="G43" s="60"/>
+      <x:c r="H43" s="60"/>
+      <x:c r="I43" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J43" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K43" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N43" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="56" t="str">
+        <x:v>orderZone</x:v>
+      </x:c>
+      <x:c r="B44" s="56" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C44" s="56" t="str">
+        <x:v>目標區域</x:v>
+      </x:c>
+      <x:c r="D44" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E44" s="56" t="str"/>
+      <x:c r="F44" s="56"/>
+      <x:c r="G44" s="56"/>
+      <x:c r="H44" s="56"/>
+      <x:c r="I44" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J44" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K44" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M44" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N44" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="60" t="str">
+        <x:v>orderResource</x:v>
+      </x:c>
+      <x:c r="B45" s="60" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C45" s="60" t="str">
+        <x:v>投入資源點數</x:v>
+      </x:c>
+      <x:c r="D45" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E45" s="60" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F45" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G45" s="60" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H45" s="60"/>
+      <x:c r="I45" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J45" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K45" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L45" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M45" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N45" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="56" t="str">
+        <x:v>orderRationale</x:v>
+      </x:c>
+      <x:c r="B46" s="56" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C46" s="56" t="str">
+        <x:v>決策理由</x:v>
+      </x:c>
+      <x:c r="D46" s="56" t="str">
+        <x:v>textarea</x:v>
+      </x:c>
+      <x:c r="E46" s="56" t="str"/>
+      <x:c r="F46" s="56"/>
+      <x:c r="G46" s="56"/>
+      <x:c r="H46" s="56"/>
+      <x:c r="I46" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J46" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K46" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L46" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N46" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="60" t="str">
+        <x:v>labIncoming</x:v>
+      </x:c>
+      <x:c r="B47" s="60" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C47" s="60" t="str">
+        <x:v>來襲目標數</x:v>
+      </x:c>
+      <x:c r="D47" s="60" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E47" s="60" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F47" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" s="60" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H47" s="60"/>
+      <x:c r="I47" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J47" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K47" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L47" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N47" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="56" t="str">
+        <x:v>labShots</x:v>
+      </x:c>
+      <x:c r="B48" s="56" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C48" s="56" t="str">
+        <x:v>配置攔截次數</x:v>
+      </x:c>
+      <x:c r="D48" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E48" s="56" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F48" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" s="56" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H48" s="56"/>
+      <x:c r="I48" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J48" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K48" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L48" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M48" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N48" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="60" t="str">
+        <x:v>labBaseP</x:v>
+      </x:c>
+      <x:c r="B49" s="60" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C49" s="60" t="str">
+        <x:v>單次基準機率</x:v>
+      </x:c>
+      <x:c r="D49" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E49" s="60" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F49" s="60" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G49" s="60" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H49" s="60"/>
+      <x:c r="I49" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J49" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K49" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M49" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N49" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="56" t="str">
+        <x:v>labDetection</x:v>
+      </x:c>
+      <x:c r="B50" s="56" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C50" s="56" t="str">
+        <x:v>偵測品質</x:v>
+      </x:c>
+      <x:c r="D50" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E50" s="56" t="str">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F50" s="56" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G50" s="56" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H50" s="56"/>
+      <x:c r="I50" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J50" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K50" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M50" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N50" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="60" t="str">
+        <x:v>labReadiness</x:v>
+      </x:c>
+      <x:c r="B51" s="60" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C51" s="60" t="str">
+        <x:v>系統準備度</x:v>
+      </x:c>
+      <x:c r="D51" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E51" s="60" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F51" s="60" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G51" s="60" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H51" s="60"/>
+      <x:c r="I51" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J51" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K51" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M51" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N51" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="56" t="str">
+        <x:v>labSea</x:v>
+      </x:c>
+      <x:c r="B52" s="56" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C52" s="56" t="str">
+        <x:v>海象</x:v>
+      </x:c>
+      <x:c r="D52" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E52" s="56" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F52" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H52" s="56"/>
+      <x:c r="I52" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J52" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K52" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L52" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M52" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N52" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="60" t="str">
+        <x:v>labJamming</x:v>
+      </x:c>
+      <x:c r="B53" s="60" t="str">
+        <x:v>simulation</x:v>
+      </x:c>
+      <x:c r="C53" s="60" t="str">
+        <x:v>干擾程度</x:v>
+      </x:c>
+      <x:c r="D53" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E53" s="60" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F53" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G53" s="60" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H53" s="60"/>
+      <x:c r="I53" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J53" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K53" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M53" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N53" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="56" t="str">
+        <x:v>stormCoa</x:v>
+      </x:c>
+      <x:c r="B54" s="56" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C54" s="56" t="str">
+        <x:v>行動方案 COA</x:v>
+      </x:c>
+      <x:c r="D54" s="56" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E54" s="56" t="str">
+        <x:v>balanced</x:v>
+      </x:c>
+      <x:c r="F54" s="56"/>
+      <x:c r="G54" s="56"/>
+      <x:c r="H54" s="56"/>
+      <x:c r="I54" s="56" t="str">
+        <x:v>["balanced","concentrated","logistics","distributed"]</x:v>
+      </x:c>
+      <x:c r="J54" s="56" t="str">
+        <x:v>["均衡韌性防衛","集中主要方向","後勤優先","分散式 ISR 與指管"]</x:v>
+      </x:c>
+      <x:c r="K54" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L54" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M54" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N54" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="60" t="str">
+        <x:v>stormReplications</x:v>
+      </x:c>
+      <x:c r="B55" s="60" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C55" s="60" t="str">
+        <x:v>重複次數</x:v>
+      </x:c>
+      <x:c r="D55" s="60" t="str">
+        <x:v>select</x:v>
+      </x:c>
+      <x:c r="E55" s="60" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F55" s="60"/>
+      <x:c r="G55" s="60"/>
+      <x:c r="H55" s="60"/>
+      <x:c r="I55" s="60" t="str">
+        <x:v>["30","100","300","500"]</x:v>
+      </x:c>
+      <x:c r="J55" s="60" t="str">
+        <x:v>["30 次：快速示範","100 次：一般分析","300 次：較穩定分布","500 次：進階比較"]</x:v>
+      </x:c>
+      <x:c r="K55" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L55" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M55" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N55" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="56" t="str">
+        <x:v>stormC2</x:v>
+      </x:c>
+      <x:c r="B56" s="56" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C56" s="56" t="str">
+        <x:v>指揮管制品質 C2</x:v>
+      </x:c>
+      <x:c r="D56" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E56" s="56" t="str">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F56" s="56" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G56" s="56" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H56" s="56"/>
+      <x:c r="I56" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J56" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K56" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L56" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M56" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N56" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="60" t="str">
+        <x:v>stormIsr</x:v>
+      </x:c>
+      <x:c r="B57" s="60" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C57" s="60" t="str">
+        <x:v>情監偵／情報品質 ISR</x:v>
+      </x:c>
+      <x:c r="D57" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E57" s="60" t="str">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F57" s="60" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G57" s="60" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H57" s="60"/>
+      <x:c r="I57" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J57" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K57" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L57" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M57" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N57" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="56" t="str">
+        <x:v>stormReadiness</x:v>
+      </x:c>
+      <x:c r="B58" s="56" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C58" s="56" t="str">
+        <x:v>資產初始準備度</x:v>
+      </x:c>
+      <x:c r="D58" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E58" s="56" t="str">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F58" s="56" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G58" s="56" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H58" s="56"/>
+      <x:c r="I58" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J58" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K58" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L58" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M58" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N58" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="60" t="str">
+        <x:v>stormSustainment</x:v>
+      </x:c>
+      <x:c r="B59" s="60" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C59" s="60" t="str">
+        <x:v>後勤持續性</x:v>
+      </x:c>
+      <x:c r="D59" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E59" s="60" t="str">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F59" s="60" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G59" s="60" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H59" s="60"/>
+      <x:c r="I59" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J59" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K59" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M59" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N59" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="56" t="str">
+        <x:v>stormMobility</x:v>
+      </x:c>
+      <x:c r="B60" s="56" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C60" s="56" t="str">
+        <x:v>機動與運輸能力</x:v>
+      </x:c>
+      <x:c r="D60" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E60" s="56" t="str">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F60" s="56" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G60" s="56" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H60" s="56"/>
+      <x:c r="I60" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J60" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K60" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L60" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M60" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N60" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="60" t="str">
+        <x:v>stormEnvironment</x:v>
+      </x:c>
+      <x:c r="B61" s="60" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C61" s="60" t="str">
+        <x:v>環境嚴苛度</x:v>
+      </x:c>
+      <x:c r="D61" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E61" s="60" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F61" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H61" s="60"/>
+      <x:c r="I61" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J61" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K61" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L61" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M61" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N61" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="56" t="str">
+        <x:v>stormPressure</x:v>
+      </x:c>
+      <x:c r="B62" s="56" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C62" s="56" t="str">
+        <x:v>對手施壓強度</x:v>
+      </x:c>
+      <x:c r="D62" s="56" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E62" s="56" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F62" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G62" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H62" s="56"/>
+      <x:c r="I62" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J62" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K62" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L62" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M62" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N62" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="60" t="str">
+        <x:v>stormCivil</x:v>
+      </x:c>
+      <x:c r="B63" s="60" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C63" s="60" t="str">
+        <x:v>民事暴露程度</x:v>
+      </x:c>
+      <x:c r="D63" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E63" s="60" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F63" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H63" s="60"/>
+      <x:c r="I63" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J63" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K63" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N63" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="56" t="str">
+        <x:v>stormSeed</x:v>
+      </x:c>
+      <x:c r="B64" s="56" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C64" s="56" t="str">
+        <x:v>隨機種子</x:v>
+      </x:c>
+      <x:c r="D64" s="56" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E64" s="56" t="str">
+        <x:v>20260727</x:v>
+      </x:c>
+      <x:c r="F64" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" s="56"/>
+      <x:c r="H64" s="56"/>
+      <x:c r="I64" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J64" s="56" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K64" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L64" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M64" s="56" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N64" s="56" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="60" t="str">
+        <x:v>stormThreshold</x:v>
+      </x:c>
+      <x:c r="B65" s="60" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C65" s="60" t="str">
+        <x:v>成功門檻</x:v>
+      </x:c>
+      <x:c r="D65" s="60" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E65" s="60" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F65" s="60" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G65" s="60" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H65" s="60"/>
+      <x:c r="I65" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="J65" s="60" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="K65" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L65" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M65" s="60" t="str">
+        <x:v>index.html</x:v>
+      </x:c>
+      <x:c r="N65" s="60" t="str">
+        <x:v>與目前介面控制項同步。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:N1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -8721,8 +12466,1462 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65758518d16646f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree23f6ddf0914faf"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="47" t="str">
+        <x:v>合成資源預設值與介面限制</x:v>
+      </x:c>
+      <x:c r="B1" s="47"/>
+      <x:c r="C1" s="47"/>
+      <x:c r="D1" s="47"/>
+      <x:c r="E1" s="47"/>
+      <x:c r="F1" s="47"/>
+      <x:c r="G1" s="47"/>
+      <x:c r="H1" s="47"/>
+      <x:c r="I1" s="47"/>
+      <x:c r="J1" s="47"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="52" t="str">
+        <x:v>resource_id</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>actor_id</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="str">
+        <x:v>類別</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="str">
+        <x:v>資源名稱</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="str">
+        <x:v>預設值</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>最小值</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="str">
+        <x:v>最大值</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="str">
+        <x:v>單位</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="str">
+        <x:v>效果說明</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="str">
+        <x:v>資料分類</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>blueAircraft</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>航空</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>藍方可用航空架次</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F4" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="56" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str">
+        <x:v>影響藍方資源平衡</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="60" t="str">
+        <x:v>blueInterceptors</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>防空</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="str">
+        <x:v>藍方攔截彈庫存</x:v>
+      </x:c>
+      <x:c r="E5" s="60" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F5" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="60" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H5" s="60" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I5" s="60" t="str">
+        <x:v>影響藍方資源平衡</x:v>
+      </x:c>
+      <x:c r="J5" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="56" t="str">
+        <x:v>blueVessels</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>海上</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="str">
+        <x:v>藍方海上巡防平台</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="56" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H6" s="56" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I6" s="56" t="str">
+        <x:v>影響藍方資源平衡</x:v>
+      </x:c>
+      <x:c r="J6" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="60" t="str">
+        <x:v>blueLogistics</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>後勤</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="str">
+        <x:v>藍方後勤補給批次</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="60" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H7" s="60" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I7" s="60" t="str">
+        <x:v>影響藍方資源平衡</x:v>
+      </x:c>
+      <x:c r="J7" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="56" t="str">
+        <x:v>blueDrones</x:v>
+      </x:c>
+      <x:c r="B8" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C8" s="56" t="str">
+        <x:v>無人系統</x:v>
+      </x:c>
+      <x:c r="D8" s="56" t="str">
+        <x:v>藍方無人機任務批次</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="56" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H8" s="56" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I8" s="56" t="str">
+        <x:v>影響藍方資源平衡與初始情報品質</x:v>
+      </x:c>
+      <x:c r="J8" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="60" t="str">
+        <x:v>starlinkNodes</x:v>
+      </x:c>
+      <x:c r="B9" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>衛星通訊</x:v>
+      </x:c>
+      <x:c r="D9" s="60" t="str">
+        <x:v>星鏈備援通訊節點</x:v>
+      </x:c>
+      <x:c r="E9" s="60" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F9" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="60" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H9" s="60" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I9" s="60" t="str">
+        <x:v>影響藍方資源平衡與初始指管品質</x:v>
+      </x:c>
+      <x:c r="J9" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="56" t="str">
+        <x:v>highAltitudePlatforms</x:v>
+      </x:c>
+      <x:c r="B10" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C10" s="56" t="str">
+        <x:v>高空通訊</x:v>
+      </x:c>
+      <x:c r="D10" s="56" t="str">
+        <x:v>高空通訊平臺</x:v>
+      </x:c>
+      <x:c r="E10" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F10" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="56" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H10" s="56" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I10" s="56" t="str">
+        <x:v>影響藍方資源平衡與初始指管品質</x:v>
+      </x:c>
+      <x:c r="J10" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="60" t="str">
+        <x:v>redAircraft</x:v>
+      </x:c>
+      <x:c r="B11" s="60" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C11" s="60" t="str">
+        <x:v>航空</x:v>
+      </x:c>
+      <x:c r="D11" s="60" t="str">
+        <x:v>紅方航空架次</x:v>
+      </x:c>
+      <x:c r="E11" s="60" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="60" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="H11" s="60" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I11" s="60" t="str">
+        <x:v>影響紅方資源平衡</x:v>
+      </x:c>
+      <x:c r="J11" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="56" t="str">
+        <x:v>redIncoming</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C12" s="56" t="str">
+        <x:v>合成目標</x:v>
+      </x:c>
+      <x:c r="D12" s="56" t="str">
+        <x:v>紅方合成來襲目標</x:v>
+      </x:c>
+      <x:c r="E12" s="56" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F12" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="56" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H12" s="56" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I12" s="56" t="str">
+        <x:v>影響紅方資源平衡</x:v>
+      </x:c>
+      <x:c r="J12" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="60" t="str">
+        <x:v>redVessels</x:v>
+      </x:c>
+      <x:c r="B13" s="60" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C13" s="60" t="str">
+        <x:v>海上</x:v>
+      </x:c>
+      <x:c r="D13" s="60" t="str">
+        <x:v>紅方海上平台</x:v>
+      </x:c>
+      <x:c r="E13" s="60" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F13" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="60" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H13" s="60" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I13" s="60" t="str">
+        <x:v>影響紅方資源平衡</x:v>
+      </x:c>
+      <x:c r="J13" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="56" t="str">
+        <x:v>redLogistics</x:v>
+      </x:c>
+      <x:c r="B14" s="56" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C14" s="56" t="str">
+        <x:v>後勤</x:v>
+      </x:c>
+      <x:c r="D14" s="56" t="str">
+        <x:v>紅方後勤補給批次</x:v>
+      </x:c>
+      <x:c r="E14" s="56" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F14" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="56" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H14" s="56" t="str">
+        <x:v>合成單位</x:v>
+      </x:c>
+      <x:c r="I14" s="56" t="str">
+        <x:v>影響紅方資源平衡</x:v>
+      </x:c>
+      <x:c r="J14" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="50" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="47" t="str">
+        <x:v>回合行動目錄與抽象裁決修正</x:v>
+      </x:c>
+      <x:c r="B1" s="47"/>
+      <x:c r="C1" s="47"/>
+      <x:c r="D1" s="47"/>
+      <x:c r="E1" s="47"/>
+      <x:c r="F1" s="47"/>
+      <x:c r="G1" s="47"/>
+      <x:c r="H1" s="47"/>
+      <x:c r="I1" s="47"/>
+      <x:c r="J1" s="47"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="52" t="str">
+        <x:v>action_id</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>actor_id</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="str">
+        <x:v>行動名稱</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="str">
+        <x:v>準備度修正</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="str">
+        <x:v>持續性修正</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>指管修正</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="str">
+        <x:v>情報修正</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="str">
+        <x:v>民事風險修正</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="str">
+        <x:v>資料分類</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="str">
+        <x:v>備註</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>ACT-BLUE-01</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>強化防空警戒</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="60" t="str">
+        <x:v>ACT-BLUE-02</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>商船護航</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="60" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F5" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="60" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="I5" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J5" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="56" t="str">
+        <x:v>ACT-BLUE-03</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>分散部署</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F6" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J6" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="60" t="str">
+        <x:v>ACT-BLUE-04</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>備援通訊</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G7" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J7" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="56" t="str">
+        <x:v>ACT-BLUE-05</x:v>
+      </x:c>
+      <x:c r="B8" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C8" s="56" t="str">
+        <x:v>後勤修復</x:v>
+      </x:c>
+      <x:c r="D8" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J8" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="60" t="str">
+        <x:v>ACT-BLUE-06</x:v>
+      </x:c>
+      <x:c r="B9" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>情報融合</x:v>
+      </x:c>
+      <x:c r="D9" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H9" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J9" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="56" t="str">
+        <x:v>ACT-BLUE-07</x:v>
+      </x:c>
+      <x:c r="B10" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C10" s="56" t="str">
+        <x:v>無人機偵察與通訊中繼</x:v>
+      </x:c>
+      <x:c r="D10" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="56" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F10" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G10" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H10" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J10" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="60" t="str">
+        <x:v>ACT-BLUE-08</x:v>
+      </x:c>
+      <x:c r="B11" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C11" s="60" t="str">
+        <x:v>星鏈與高空平臺備援通訊</x:v>
+      </x:c>
+      <x:c r="D11" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="60" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F11" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G11" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J11" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="56" t="str">
+        <x:v>ACT-BLUE-09</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C12" s="56" t="str">
+        <x:v>能源配給與電網調度</x:v>
+      </x:c>
+      <x:c r="D12" s="56" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="E12" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F12" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G12" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="56" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="I12" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J12" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="60" t="str">
+        <x:v>ACT-BLUE-10</x:v>
+      </x:c>
+      <x:c r="B13" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C13" s="60" t="str">
+        <x:v>經濟持續運作協調</x:v>
+      </x:c>
+      <x:c r="D13" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F13" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G13" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="60" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="I13" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J13" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="56" t="str">
+        <x:v>ACT-RED-01</x:v>
+      </x:c>
+      <x:c r="B14" s="56" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C14" s="56" t="str">
+        <x:v>增加空中施壓</x:v>
+      </x:c>
+      <x:c r="D14" s="56" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="E14" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I14" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J14" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="60" t="str">
+        <x:v>ACT-RED-02</x:v>
+      </x:c>
+      <x:c r="B15" s="60" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C15" s="60" t="str">
+        <x:v>海上臨檢演示</x:v>
+      </x:c>
+      <x:c r="D15" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="60" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F15" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I15" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J15" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="56" t="str">
+        <x:v>ACT-RED-03</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C16" s="56" t="str">
+        <x:v>電磁壓制</x:v>
+      </x:c>
+      <x:c r="D16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G16" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H16" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I16" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J16" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="60" t="str">
+        <x:v>ACT-RED-04</x:v>
+      </x:c>
+      <x:c r="B17" s="60" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C17" s="60" t="str">
+        <x:v>遠程火力展示</x:v>
+      </x:c>
+      <x:c r="D17" s="60" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="E17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I17" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J17" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="56" t="str">
+        <x:v>ACT-RED-05</x:v>
+      </x:c>
+      <x:c r="B18" s="56" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C18" s="56" t="str">
+        <x:v>調整封控區</x:v>
+      </x:c>
+      <x:c r="D18" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J18" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="60" t="str">
+        <x:v>ACT-RED-06</x:v>
+      </x:c>
+      <x:c r="B19" s="60" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C19" s="60" t="str">
+        <x:v>外交訊息操作</x:v>
+      </x:c>
+      <x:c r="D19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H19" s="60" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="I19" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J19" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="56" t="str">
+        <x:v>ACT-RED-07</x:v>
+      </x:c>
+      <x:c r="B20" s="56" t="str">
+        <x:v>RED</x:v>
+      </x:c>
+      <x:c r="C20" s="56" t="str">
+        <x:v>海警與海上民兵執法封控</x:v>
+      </x:c>
+      <x:c r="D20" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H20" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I20" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J20" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="60" t="str">
+        <x:v>ACT-AMBER-01</x:v>
+      </x:c>
+      <x:c r="B21" s="60" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C21" s="60" t="str">
+        <x:v>提供ISR支援</x:v>
+      </x:c>
+      <x:c r="D21" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H21" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J21" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="56" t="str">
+        <x:v>ACT-AMBER-02</x:v>
+      </x:c>
+      <x:c r="B22" s="56" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C22" s="56" t="str">
+        <x:v>提升後勤準備</x:v>
+      </x:c>
+      <x:c r="D22" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F22" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J22" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="60" t="str">
+        <x:v>ACT-AMBER-03</x:v>
+      </x:c>
+      <x:c r="B23" s="60" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C23" s="60" t="str">
+        <x:v>網路防護支援</x:v>
+      </x:c>
+      <x:c r="D23" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F23" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G23" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J23" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="56" t="str">
+        <x:v>ACT-AMBER-04</x:v>
+      </x:c>
+      <x:c r="B24" s="56" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C24" s="56" t="str">
+        <x:v>外交協調</x:v>
+      </x:c>
+      <x:c r="D24" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="56" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="I24" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J24" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="60" t="str">
+        <x:v>ACT-AMBER-05</x:v>
+      </x:c>
+      <x:c r="B25" s="60" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C25" s="60" t="str">
+        <x:v>遠距海上存在</x:v>
+      </x:c>
+      <x:c r="D25" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H25" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I25" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J25" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="56" t="str">
+        <x:v>ACT-AMBER-06</x:v>
+      </x:c>
+      <x:c r="B26" s="56" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C26" s="56" t="str">
+        <x:v>人道支援準備</x:v>
+      </x:c>
+      <x:c r="D26" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F26" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="56" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="I26" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J26" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="60" t="str">
+        <x:v>ACT-AMBER-07</x:v>
+      </x:c>
+      <x:c r="B27" s="60" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C27" s="60" t="str">
+        <x:v>提供衛星與高空通訊支援</x:v>
+      </x:c>
+      <x:c r="D27" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G27" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J27" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="56" t="str">
+        <x:v>ACT-AMBER-08</x:v>
+      </x:c>
+      <x:c r="B28" s="56" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C28" s="56" t="str">
+        <x:v>多國商船護航協調</x:v>
+      </x:c>
+      <x:c r="D28" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F28" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G28" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="56" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="I28" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J28" s="56" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="60" t="str">
+        <x:v>ACT-AMBER-09</x:v>
+      </x:c>
+      <x:c r="B29" s="60" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C29" s="60" t="str">
+        <x:v>工業補充與供應鏈動員</x:v>
+      </x:c>
+      <x:c r="D29" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F29" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="60" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="I29" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+      <x:c r="J29" s="60" t="str">
+        <x:v>與 app.js ACTIONS 同步；數值為抽象教育裁決修正。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="56" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="47" t="str">
+        <x:v>LLM 供應商、模型與 Endpoint 預設值</x:v>
+      </x:c>
+      <x:c r="B1" s="47"/>
+      <x:c r="C1" s="47"/>
+      <x:c r="D1" s="47"/>
+      <x:c r="E1" s="47"/>
+      <x:c r="F1" s="47"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="52" t="str">
+        <x:v>provider_id</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>供應商</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="str">
+        <x:v>預設模型</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="str">
+        <x:v>API Endpoint</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="str">
+        <x:v>模型清單JSON</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>API Key 保存政策</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>gemini</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>Gemini</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>gemini-3.5-flash</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>https://generativelanguage.googleapis.com/v1beta</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="str">
+        <x:v>["gemini-3.5-flash","gemini-3.6-flash"]</x:v>
+      </x:c>
+      <x:c r="F4" s="56" t="str">
+        <x:v>瀏覽器本機；資料庫不保存</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="60" t="str">
+        <x:v>openai</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>gpt-5.5</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="str">
+        <x:v>https://api.openai.com/v1</x:v>
+      </x:c>
+      <x:c r="E5" s="60" t="str">
+        <x:v>["gpt-5.4-mini","gpt-5.5","gpt-5.6"]</x:v>
+      </x:c>
+      <x:c r="F5" s="60" t="str">
+        <x:v>瀏覽器本機；資料庫不保存</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="56" t="str">
+        <x:v>claude</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>Claude</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>claude-sonnet-4-20250514</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="str">
+        <x:v>https://api.anthropic.com/v1</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="str">
+        <x:v>["claude-sonnet-4-20250514"]</x:v>
+      </x:c>
+      <x:c r="F6" s="56" t="str">
+        <x:v>瀏覽器本機；資料庫不保存</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="60" t="str">
+        <x:v>cgu</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="str">
+        <x:v>長庚 CGU LLM API</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>gpt-5.4-mini</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="str">
+        <x:v>https://air.cgu.edu.tw/cgullmapi/v1</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="str">
+        <x:v>["gpt-5.4-mini","gpt-5.5","gpt-5.6"]</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="str">
+        <x:v>瀏覽器本機；資料庫不保存</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -8888,7 +14087,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcff7223721644b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8926a1903d84d37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8912,84 +14111,399 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>合成情境主檔</x:v>
-      </x:c>
+      <x:c r="A1" s="61" t="str">
+        <x:v>九種內建合成情境主檔</x:v>
+      </x:c>
+      <x:c r="B1" s="46"/>
+      <x:c r="C1" s="46"/>
+      <x:c r="D1" s="46"/>
+      <x:c r="E1" s="46"/>
+      <x:c r="F1" s="46"/>
+      <x:c r="G1" s="46"/>
+      <x:c r="H1" s="46"/>
+      <x:c r="I1" s="46"/>
+      <x:c r="J1" s="46"/>
+      <x:c r="K1" s="46"/>
+      <x:c r="L1" s="46"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="62" t="str">
         <x:v>scenario_id</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="62" t="str">
         <x:v>scenario_name</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="62" t="str">
+        <x:v>template_key</x:v>
+      </x:c>
+      <x:c r="D3" s="62" t="str">
+        <x:v>difficulty</x:v>
+      </x:c>
+      <x:c r="E3" s="62" t="str">
+        <x:v>turns</x:v>
+      </x:c>
+      <x:c r="F3" s="62" t="str">
+        <x:v>hours_per_turn</x:v>
+      </x:c>
+      <x:c r="G3" s="62" t="str">
+        <x:v>time_range</x:v>
+      </x:c>
+      <x:c r="H3" s="62" t="str">
+        <x:v>focus</x:v>
+      </x:c>
+      <x:c r="I3" s="62" t="str">
+        <x:v>amber_support</x:v>
+      </x:c>
+      <x:c r="J3" s="62" t="str">
+        <x:v>weather_preset</x:v>
+      </x:c>
+      <x:c r="K3" s="62" t="str">
+        <x:v>turn_order_mode</x:v>
+      </x:c>
+      <x:c r="L3" s="62" t="str">
         <x:v>data_class</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>level</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="str">
-        <x:v>turns</x:v>
-      </x:c>
-      <x:c r="F3" s="14" t="str">
-        <x:v>hours_per_turn</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>time_range</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="str">
-        <x:v>blue_actor</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="str">
-        <x:v>red_actor</x:v>
-      </x:c>
-      <x:c r="J3" s="14" t="str">
-        <x:v>amber_actor</x:v>
-      </x:c>
-      <x:c r="K3" s="14" t="str">
-        <x:v>learning_objectives</x:v>
-      </x:c>
-      <x:c r="L3" s="14" t="str">
-        <x:v>safety_note</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="36" t="str">
-        <x:v>TS-EDU-001</x:v>
-      </x:c>
-      <x:c r="B4" s="36" t="str">
+      <x:c r="A4" s="56" t="str">
+        <x:v>TS-TPL-001</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
         <x:v>海峽警戒與有限封控：72小時聯合決策演練</x:v>
       </x:c>
-      <x:c r="C4" s="36" t="str">
-        <x:v>教育兵推/合成資料</x:v>
-      </x:c>
-      <x:c r="D4" s="36" t="str">
-        <x:v>作戰層級</x:v>
-      </x:c>
-      <x:c r="E4" s="36" t="n">
+      <x:c r="C4" s="56" t="str">
+        <x:v>blockade</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F4" s="36" t="n">
+      <x:c r="F4" s="56" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G4" s="36" t="str">
+      <x:c r="G4" s="56" t="str">
         <x:v>T+0至T+72</x:v>
       </x:c>
-      <x:c r="H4" s="36" t="str">
-        <x:v>藍方（臺灣）</x:v>
-      </x:c>
-      <x:c r="I4" s="36" t="str">
-        <x:v>紅方（中國大陸）</x:v>
-      </x:c>
-      <x:c r="J4" s="36" t="str">
-        <x:v>琥珀方（美軍支援）</x:v>
-      </x:c>
-      <x:c r="K4" s="36" t="str">
-        <x:v>訓練情勢判斷、資源配置、後勤持續性、情報不確定性與課後檢討</x:v>
-      </x:c>
-      <x:c r="L4" s="36" t="str">
-        <x:v>所有兵力、效能、庫存、損失與位置均為合成示範；區域不含精確座標；不得用於真實作戰規劃。</x:v>
+      <x:c r="H4" s="56" t="str">
+        <x:v>joint</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L4" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="60" t="str">
+        <x:v>TS-TPL-002</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="str">
+        <x:v>多軸空情與分層防護：48小時資源配置演練</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>airdefense</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="E5" s="60" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F5" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G5" s="60" t="str">
+        <x:v>T+0至T+48</x:v>
+      </x:c>
+      <x:c r="H5" s="60" t="str">
+        <x:v>airdefense</x:v>
+      </x:c>
+      <x:c r="I5" s="60" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="J5" s="60" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="K5" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L5" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="56" t="str">
+        <x:v>TS-TPL-003</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>港口延誤與後勤韌性：96小時持續性演練</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>logistics</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F6" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G6" s="56" t="str">
+        <x:v>T+0至T+96</x:v>
+      </x:c>
+      <x:c r="H6" s="56" t="str">
+        <x:v>logistics</x:v>
+      </x:c>
+      <x:c r="I6" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="J6" s="56" t="str">
+        <x:v>adverse</x:v>
+      </x:c>
+      <x:c r="K6" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L6" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="60" t="str">
+        <x:v>TS-TPL-004</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="str">
+        <x:v>灰色地帶與資訊迷霧：跨域判讀演練</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>grayzone</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="60" t="str">
+        <x:v>T+0至T+60</x:v>
+      </x:c>
+      <x:c r="H7" s="60" t="str">
+        <x:v>intelligence</x:v>
+      </x:c>
+      <x:c r="I7" s="60" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="J7" s="60" t="str">
+        <x:v>stable</x:v>
+      </x:c>
+      <x:c r="K7" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L7" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="56" t="str">
+        <x:v>TS-TPL-005</x:v>
+      </x:c>
+      <x:c r="B8" s="56" t="str">
+        <x:v>人道疏散與民事協調：危機韌性演練</x:v>
+      </x:c>
+      <x:c r="C8" s="56" t="str">
+        <x:v>humanitarian</x:v>
+      </x:c>
+      <x:c r="D8" s="56" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="56" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G8" s="56" t="str">
+        <x:v>T+0至T+60</x:v>
+      </x:c>
+      <x:c r="H8" s="56" t="str">
+        <x:v>civil</x:v>
+      </x:c>
+      <x:c r="I8" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="J8" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="K8" s="56" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L8" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="60" t="str">
+        <x:v>TS-TPL-006</x:v>
+      </x:c>
+      <x:c r="B9" s="60" t="str">
+        <x:v>危機降溫與外交窗口：升級控制演練</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>deescalation</x:v>
+      </x:c>
+      <x:c r="D9" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="E9" s="60" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F9" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G9" s="60" t="str">
+        <x:v>T+0至T+48</x:v>
+      </x:c>
+      <x:c r="H9" s="60" t="str">
+        <x:v>diplomacy</x:v>
+      </x:c>
+      <x:c r="I9" s="60" t="str">
+        <x:v>indirect</x:v>
+      </x:c>
+      <x:c r="J9" s="60" t="str">
+        <x:v>stable</x:v>
+      </x:c>
+      <x:c r="K9" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L9" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="56" t="str">
+        <x:v>TS-TPL-007</x:v>
+      </x:c>
+      <x:c r="B10" s="56" t="str">
+        <x:v>CSIS《燈火管制》（2025）：封鎖、護航與能源韌性</x:v>
+      </x:c>
+      <x:c r="C10" s="56" t="str">
+        <x:v>csis_blackout_2025</x:v>
+      </x:c>
+      <x:c r="D10" s="56" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="E10" s="56" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F10" s="56" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="56" t="str">
+        <x:v>T+0至T+240</x:v>
+      </x:c>
+      <x:c r="H10" s="56" t="str">
+        <x:v>logistics</x:v>
+      </x:c>
+      <x:c r="I10" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="J10" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="K10" s="56" t="str">
+        <x:v>red_first</x:v>
+      </x:c>
+      <x:c r="L10" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="60" t="str">
+        <x:v>TS-TPL-008</x:v>
+      </x:c>
+      <x:c r="B11" s="60" t="str">
+        <x:v>CSIS &amp; MIT（2024）：傳統戰局與核升級風險</x:v>
+      </x:c>
+      <x:c r="C11" s="60" t="str">
+        <x:v>csis_mit_nuclear_2024</x:v>
+      </x:c>
+      <x:c r="D11" s="60" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="E11" s="60" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F11" s="60" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G11" s="60" t="str">
+        <x:v>T+0至T+72</x:v>
+      </x:c>
+      <x:c r="H11" s="60" t="str">
+        <x:v>diplomacy</x:v>
+      </x:c>
+      <x:c r="I11" s="60" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="J11" s="60" t="str">
+        <x:v>stable</x:v>
+      </x:c>
+      <x:c r="K11" s="60" t="str">
+        <x:v>simultaneous</x:v>
+      </x:c>
+      <x:c r="L11" s="60" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="56" t="str">
+        <x:v>TS-TPL-009</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="str">
+        <x:v>美國國會 × CNAS：一週彈藥耗盡與全球經濟衝擊</x:v>
+      </x:c>
+      <x:c r="C12" s="56" t="str">
+        <x:v>cnas_policy_war</x:v>
+      </x:c>
+      <x:c r="D12" s="56" t="str">
+        <x:v>advanced</x:v>
+      </x:c>
+      <x:c r="E12" s="56" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="56" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G12" s="56" t="str">
+        <x:v>T+0至T+168</x:v>
+      </x:c>
+      <x:c r="H12" s="56" t="str">
+        <x:v>joint</x:v>
+      </x:c>
+      <x:c r="I12" s="56" t="str">
+        <x:v>limited</x:v>
+      </x:c>
+      <x:c r="J12" s="56" t="str">
+        <x:v>variable</x:v>
+      </x:c>
+      <x:c r="K12" s="56" t="str">
+        <x:v>red_first</x:v>
+      </x:c>
+      <x:c r="L12" s="56" t="str">
+        <x:v>EDUCATIONAL_SYNTHETIC</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8998,7 +14512,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc242325072946f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0960142678484114"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9126,7 +14640,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6a0dff7b0724edb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8723dd74037747c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9390,7 +14904,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R993e858e87b44ac2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22c9cd665e204df0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10213,6 +15727,120 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L23" s="36" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="56" t="str">
+        <x:v>B-UAS-01</x:v>
+      </x:c>
+      <x:c r="B24" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C24" s="56" t="str">
+        <x:v>無人機偵察與通訊中繼群</x:v>
+      </x:c>
+      <x:c r="D24" s="56" t="str">
+        <x:v>無人系統</x:v>
+      </x:c>
+      <x:c r="E24" s="56" t="str">
+        <x:v>Z-ISL</x:v>
+      </x:c>
+      <x:c r="F24" s="56" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G24" s="56" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H24" s="56" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I24" s="56" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="J24" s="56" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K24" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L24" s="56" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="60" t="str">
+        <x:v>B-COM-01</x:v>
+      </x:c>
+      <x:c r="B25" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="C25" s="60" t="str">
+        <x:v>韌性衛星通訊節點群</x:v>
+      </x:c>
+      <x:c r="D25" s="60" t="str">
+        <x:v>衛星通訊</x:v>
+      </x:c>
+      <x:c r="E25" s="60" t="str">
+        <x:v>Z-ISL</x:v>
+      </x:c>
+      <x:c r="F25" s="60" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G25" s="60" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H25" s="60" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I25" s="60" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="J25" s="60" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K25" s="60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L25" s="60" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="56" t="str">
+        <x:v>A-HAP-01</x:v>
+      </x:c>
+      <x:c r="B26" s="56" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="C26" s="56" t="str">
+        <x:v>衛星與高空通訊支援群</x:v>
+      </x:c>
+      <x:c r="D26" s="56" t="str">
+        <x:v>高空通訊</x:v>
+      </x:c>
+      <x:c r="E26" s="56" t="str">
+        <x:v>Z-REAR</x:v>
+      </x:c>
+      <x:c r="F26" s="56" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G26" s="56" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H26" s="56" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I26" s="56" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J26" s="56" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K26" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L26" s="56" t="str">
         <x:v>合成</x:v>
       </x:c>
     </x:row>
@@ -10292,7 +15920,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63587780d68d4441"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a79da9c9fcd45c5"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -10984,13 +16612,127 @@
         <x:v>教學用民事模型</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="56" t="str">
+        <x:v>CAP-016</x:v>
+      </x:c>
+      <x:c r="B19" s="56" t="str">
+        <x:v>無人機任務系統P</x:v>
+      </x:c>
+      <x:c r="C19" s="56" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="D19" s="56" t="str">
+        <x:v>無人系統</x:v>
+      </x:c>
+      <x:c r="E19" s="56" t="str">
+        <x:v>偵察、通訊中繼與資訊支援</x:v>
+      </x:c>
+      <x:c r="F19" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G19" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I19" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J19" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K19" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L19" s="56" t="str">
+        <x:v>能力指數1-5；不對應真實型號、數量或性能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="60" t="str">
+        <x:v>CAP-017</x:v>
+      </x:c>
+      <x:c r="B20" s="60" t="str">
+        <x:v>星鏈備援通訊系統Q</x:v>
+      </x:c>
+      <x:c r="C20" s="60" t="str">
+        <x:v>BLUE</x:v>
+      </x:c>
+      <x:c r="D20" s="60" t="str">
+        <x:v>衛星通訊</x:v>
+      </x:c>
+      <x:c r="E20" s="60" t="str">
+        <x:v>分散式備援通訊與指揮韌性</x:v>
+      </x:c>
+      <x:c r="F20" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G20" s="60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H20" s="60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I20" s="60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J20" s="60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K20" s="60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L20" s="60" t="str">
+        <x:v>合成節點模型；不含軌道、站位或真實容量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="56" t="str">
+        <x:v>CAP-018</x:v>
+      </x:c>
+      <x:c r="B21" s="56" t="str">
+        <x:v>高空通訊平臺R</x:v>
+      </x:c>
+      <x:c r="C21" s="56" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="D21" s="56" t="str">
+        <x:v>高空通訊</x:v>
+      </x:c>
+      <x:c r="E21" s="56" t="str">
+        <x:v>廣域通訊中繼與備援連接</x:v>
+      </x:c>
+      <x:c r="F21" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G21" s="56" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H21" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I21" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J21" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K21" s="56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L21" s="56" t="str">
+        <x:v>合成平臺模型；不含真實型號、站位或性能</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dbe47cfe0544c65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51e5f21b70824912"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13846,7 +19588,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d3304fa39494fac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53800f02aee6461e"/>
   </x:tableParts>
 </x:worksheet>
 </file>